--- a/hira_material_automation/output/monthly/202601_202610__epidural_adhesion_barrier__900129__normalized.xlsx
+++ b/hira_material_automation/output/monthly/202601_202610__epidural_adhesion_barrier__900129__normalized.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-05T00:23:27</t>
+          <t>2026-10-15T00:17:05</t>
         </is>
       </c>
     </row>
@@ -834,7 +834,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>827d0feaa618c6a6d30ad04ad40b0a42eff08a7a2a10e5ca0699dfa1161b2da0</t>
+          <t>fb4aac112739aaa7642c8cd0d857bf44c4dccc35c30b07e9f76c2d0123c0ae34</t>
         </is>
       </c>
     </row>
